--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.20561281664624</v>
+        <v>5.720912082705014</v>
       </c>
       <c r="D2" t="n">
-        <v>24.34679552602135</v>
+        <v>3.956354272978469</v>
       </c>
       <c r="E2" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F2" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.69865327192937</v>
+        <v>9.376031156688523</v>
       </c>
       <c r="D3" t="n">
-        <v>47.59716016737259</v>
+        <v>7.734538527198046</v>
       </c>
       <c r="E3" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F3" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.09959311393916</v>
+        <v>4.891183881015113</v>
       </c>
       <c r="D4" t="n">
-        <v>17.93809296716764</v>
+        <v>2.914940107164742</v>
       </c>
       <c r="E4" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F4" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.230313930071</v>
+        <v>9.624926013636538</v>
       </c>
       <c r="D5" t="n">
-        <v>50.38053115771563</v>
+        <v>8.18683631312879</v>
       </c>
       <c r="E5" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F5" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.7911541986667</v>
+        <v>7.278562557283339</v>
       </c>
       <c r="D6" t="n">
-        <v>37.92020499539031</v>
+        <v>6.162033311750927</v>
       </c>
       <c r="E6" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F6" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.06507869262735</v>
+        <v>4.560575287551944</v>
       </c>
       <c r="D7" t="n">
-        <v>22.49844408347709</v>
+        <v>3.655997163565028</v>
       </c>
       <c r="E7" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F7" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.036546552187219</v>
+        <v>0.6559388147304231</v>
       </c>
       <c r="D8" t="n">
-        <v>9.339194689586979</v>
+        <v>1.517619137057884</v>
       </c>
       <c r="E8" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F8" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.37385113287844</v>
+        <v>3.148250809092746</v>
       </c>
       <c r="D9" t="n">
-        <v>24.99442198584446</v>
+        <v>4.061593572699726</v>
       </c>
       <c r="E9" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F9" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.72327126330158</v>
+        <v>5.317531580286507</v>
       </c>
       <c r="D10" t="n">
-        <v>31.94574951282114</v>
+        <v>5.191184295833436</v>
       </c>
       <c r="E10" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F10" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.20743687382041</v>
+        <v>3.933708491995817</v>
       </c>
       <c r="D11" t="n">
-        <v>24.56735368024651</v>
+        <v>3.992194973040058</v>
       </c>
       <c r="E11" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F11" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.70658401785795</v>
+        <v>7.752319902901917</v>
       </c>
       <c r="D12" t="n">
-        <v>7.889726020222975</v>
+        <v>1.282080478286233</v>
       </c>
       <c r="E12" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F12" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.32338839829673</v>
+        <v>3.140050614723219</v>
       </c>
       <c r="D13" t="n">
-        <v>18.6509567049518</v>
+        <v>3.030780464554667</v>
       </c>
       <c r="E13" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F13" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.65158116143346</v>
+        <v>7.093381938732938</v>
       </c>
       <c r="D14" t="n">
-        <v>8.681431541763072</v>
+        <v>1.410732625536499</v>
       </c>
       <c r="E14" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F14" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.74221935835073</v>
+        <v>6.620610645731994</v>
       </c>
       <c r="D15" t="n">
-        <v>15.49552591727072</v>
+        <v>2.518022961556492</v>
       </c>
       <c r="E15" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F15" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.12017243659846</v>
+        <v>2.457028020947249</v>
       </c>
       <c r="D16" t="n">
-        <v>15.12017243659846</v>
+        <v>2.457028020947249</v>
       </c>
       <c r="E16" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F16" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>47.95105589287252</v>
+        <v>7.792046582591786</v>
       </c>
       <c r="D17" t="n">
-        <v>9.900839560322991</v>
+        <v>1.608886428552486</v>
       </c>
       <c r="E17" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F17" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>62.91401227214545</v>
+        <v>10.22352699422364</v>
       </c>
       <c r="D18" t="n">
-        <v>15.05436747183532</v>
+        <v>2.44633471417324</v>
       </c>
       <c r="E18" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F18" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>56.17934009098704</v>
+        <v>9.129142764785394</v>
       </c>
       <c r="D19" t="n">
-        <v>9.579346196055523</v>
+        <v>1.556643756859023</v>
       </c>
       <c r="E19" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F19" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>31.86967505582103</v>
+        <v>5.178822196570917</v>
       </c>
       <c r="D20" t="n">
-        <v>32.54066682750963</v>
+        <v>5.287858359470314</v>
       </c>
       <c r="E20" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F20" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>20.77333456235574</v>
+        <v>3.375666866382808</v>
       </c>
       <c r="D21" t="n">
-        <v>20.77333456235574</v>
+        <v>3.375666866382808</v>
       </c>
       <c r="E21" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F21" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>27.60090742535375</v>
+        <v>4.485147456619985</v>
       </c>
       <c r="D22" t="n">
-        <v>27.60090742535375</v>
+        <v>4.485147456619985</v>
       </c>
       <c r="E22" t="n">
-        <v>15.67210656694818</v>
+        <v>2.54671731712908</v>
       </c>
       <c r="F22" t="n">
-        <v>11.90398886725153</v>
+        <v>1.934398190928374</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
